--- a/oos_analysis_report.xlsx
+++ b/oos_analysis_report.xlsx
@@ -22,8 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -177,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -197,6 +198,9 @@
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -204,6 +208,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,10 +231,10 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -604,8 +611,8 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="31" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="4" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -620,7 +627,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated on 2026-05-23 23:23. AI-Assisted Inventory Integrity Engine.</t>
+          <t>Generated on 2026-05-23 23:45. AI-Assisted Inventory Integrity Engine.</t>
         </is>
       </c>
     </row>
@@ -694,6 +701,11 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
+          <t>Stockout_Probability</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
           <t>Severity_Level</t>
         </is>
       </c>
@@ -723,38 +735,44 @@
       <c r="F10" s="7" t="n">
         <v>-10</v>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="9" t="n">
+        <v>0.7665428052201496</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>SKU-002</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="11" t="n">
         <v>-5</v>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G11" s="13" t="n">
+        <v>0.6453058878107172</v>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -785,38 +803,44 @@
       <c r="F12" s="7" t="n">
         <v>-10</v>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="9" t="n">
+        <v>0.90118146387693</v>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>SKU-004</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="11" t="n">
         <v>-6</v>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G13" s="13" t="n">
+        <v>0.9772499379857481</v>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -847,7 +871,10 @@
       <c r="F14" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="9" t="n">
+        <v>0.9319814058938808</v>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -923,37 +950,37 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>Under-ordering / Small Batch</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="inlineStr">
-        <is>
-          <t>Safety stock was not sufficient to cover demand during lead time.</t>
-        </is>
-      </c>
-      <c r="G3" s="14" t="inlineStr">
-        <is>
-          <t>The SKU-001 (Premium Wireless Headphones) is predicted to go out of stock on 2026-06-21, with current stock at 200 units and a safety stock of 50 units. The reorder point is set at 80 units, and the reorder quantity is 150 units, with a supplier lead time of 7 days. The daily demand is consistently 12 units. As we analyze the daily inventory simulation, we see that the stock level decreases steadily, reaching the reorder point on 2026-06-14. However, the outstanding order (PO-991) for 150 units is only expected to arrive on 2026-06-04, which temporarily boosts stock levels to 194 units. Despite this, the daily demand continues to deplete the inventory. By 2026-06-20, the stock level drops to 14 units, and by the next day, it falls to -10 units, indicating a stockout. The primary issue is that the reorder quantity of 150 units was insufficient to cover the demand during the lead time, leading to an eventual negative stock situation. The safety stock was also not adequate to buffer against the demand during this period.</t>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>Severe Initial Understocking</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>The safety stock of 50 units was insufficient to buffer against demand volatility of 2.50 units/day, especially with a steady demand of 12 units/day. Lead-time volatility also contributed to uncertainty in stock availability.</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>The analysis of SKU-001 reveals a critical issue of severe initial understocking. With a current stock of 200 units and a daily demand of 12 units, the inventory was projected to deplete steadily over the days leading up to the predicted OOS date. The safety stock of 50 units was inadequate given the daily demand and the demand volatility of 2.50 units/day. This volatility indicates that actual demand could exceed the average, further straining the available stock. Additionally, while there is an outstanding pipeline order of 150 units expected to arrive on June 4, the lead time has a standard deviation of 1.20 days, introducing uncertainty into the delivery schedule. If the delivery is delayed, the stock will not be replenished in time to meet the ongoing demand. By June 21, the stock is projected to drop to -10 units, with a stockout probability of 76.7%, indicating a high risk of stockout due to the combination of insufficient initial stock, inadequate safety stock, and the potential for lead-time delays. Therefore, the primary root cause is identified as severe initial understocking, compounded by demand volatility and lead-time uncertainty.</t>
         </is>
       </c>
     </row>
@@ -976,54 +1003,54 @@
       <c r="D4" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>Severe Initial Understocking</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t>Demand unexpectedly surged on June 2, exceeding forecasted levels.</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>The analysis of SKU-002 (Ergonomic Office Chair) reveals a critical issue of severe initial understocking. The current stock level of 120 units was insufficient to meet the demand forecasted for the upcoming days. With a daily demand of 8 units, the stock would have been depleted by June 1, leaving only 40 units, which is exactly equal to the safety stock level. On June 2, however, demand surged to 45 units, resulting in a negative stock level of -5 units by the end of the day. The reorder point was set at 60 units, which was not triggered in time due to the low stock levels leading into the demand spike. Additionally, the outstanding purchase order (PO-992) for 100 units has a delivery date of June 12, which is too late to mitigate the immediate out-of-stock situation. The combination of these factors led to a critical stockout event, with the inventory projected to remain negative for several days until the new stock arrives.</t>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>High daily demand volatility (4 units/day) combined with a low safety stock (40 units) exacerbated the risk of stockouts.</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>The analysis reveals that the initial stock of 120 units was insufficient to cover the demand surge that occurred on June 2, where the expected demand jumped to 45 units, significantly exceeding the average daily demand of 8 units. The safety stock of 40 units was not adequate to buffer against the high demand volatility of 4 units/day. Additionally, the supplier lead time of 10 days with a standard deviation of 2 days means that any delays in receiving the outstanding order (PO-992) could further exacerbate the stockout situation. The combination of these factors led to a stockout probability of 64.5% on the predicted OOS date, indicating a high risk of running out of stock. As the inventory levels decreased daily without any incoming receipts until June 12, the stock went negative by June 2, confirming the severe initial understocking as the primary root cause of the impending stockout event.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Supplier Lead-Time Delay</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>Insufficient starting stock and high daily demand contributed to rapid depletion.</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>The SKU-003 (Organic Matcha Tea Powder 100g) is predicted to go out of stock on 2026-05-28, with current stock at 50 units, which is only 20 units above the safety stock of 30 units. The reorder point is set at 60 units, meaning that no reorder was triggered despite the stock being critically low. The daily demand is consistent at 10 units, leading to a depletion of stock from 50 units down to 0 units by the predicted OOS date. Furthermore, there is an outstanding purchase order (PO-993) for 120 units, but the expected delivery date is delayed until 2026-06-08, which is 11 days after the OOS event. This delay in supplier lead time, combined with the insufficient starting stock and the high daily demand, results in a negative inventory situation starting from 2026-05-29, where the stock goes down to -10 units and continues to decline until the delayed order arrives. Thus, the primary root cause of the upcoming OOS event is the supplier lead-time delay.</t>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Severe Initial Understocking</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>The reorder point was set too low, and the outstanding order is delayed, compounding the issue. Demand volatility also contributes to the risk of stockouts.</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>The analysis of SKU-003 reveals a critical inventory situation leading to an expected stockout date of 2026-05-28, with a stockout probability of 90.1%. The current stock of 50 units is insufficient given the daily demand of 10 units, which results in a rapid depletion of stock. The safety stock of 30 units does not provide adequate buffer against the consistent daily demand, particularly when considering the demand volatility of 3.00 units/day. This high volatility indicates that actual demand can fluctuate significantly, increasing the risk of stockouts. Furthermore, the reorder point is set at 60 units, which is too low given the average daily demand and the lead time of 12 days (with a volatility of 2.50 days). The outstanding purchase order (PO-993) for 120 units is delayed, with an expected delivery date of 2026-06-08, which is too late to prevent the stockout. As a result, the combination of severe initial understocking, a low reorder point, and the delayed supplier lead time has led to a high probability of stockout and negative inventory levels shortly after the predicted OOS date.</t>
         </is>
       </c>
     </row>
@@ -1046,54 +1073,54 @@
       <c r="D6" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>Severe Initial Understocking</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>High daily demand of 8 units with no incoming stock.</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>The analysis of SKU-004 (Smart Fitness Tracker Band) reveals a critical understocking issue leading to an impending out-of-stock (OOS) event. As of May 23, 2026, the current stock was only 10 units, significantly below the safety stock level of 40 units and the reorder point of 50 units. With a daily demand of 8 units, the stock was projected to deplete rapidly. On May 24, the stock would drop to 2 units after fulfilling the day's demand, and by May 25, it would fall to -6 units, indicating a negative inventory situation. The absence of any outstanding pipeline orders exacerbates the issue, as there are no incoming receipts to replenish stock. The supplier lead time of 5 days means that even if an order were placed immediately, it would not arrive in time to prevent the OOS event. Therefore, the combination of severe initial understocking and high daily demand has led to a critical inventory shortfall, resulting in the predicted OOS on May 24, 2026.</t>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>High daily demand volatility (2.00 units/day) coupled with a low safety stock (40 units) exacerbated the situation, leading to a rapid depletion of stock.</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>The analysis of SKU-004 reveals a critical issue of severe initial understocking. With only 10 units in stock and a reorder point set at 50 units, the inventory was critically low before the demand period began. The daily demand of 8 units, combined with a high demand volatility of 2.00 units/day, indicates that demand can fluctuate significantly, increasing the risk of stockouts. On the predicted OOS date of 2026-05-24, the expected stockout probability soared to 97.7%, primarily due to the insufficient starting stock. The safety stock of 40 units was inadequate to buffer against the daily demand, especially given the volatility. Additionally, there were no outstanding pipeline orders to replenish stock, which meant that no new inventory would arrive to mitigate the demand. The combination of these factors led to a rapid decline in stock levels, resulting in a negative ending stock of -6 units by the next day, confirming the severity of the understocking issue.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>Severe Initial Understocking</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>High daily demand of 5 units with no incoming receipts.</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>The analysis of SKU-005 (Biodegradable Bamboo Coffee Mug) reveals a critical issue of severe initial understocking. As of May 23, 2026, the starting stock was only 15 units, which is significantly below the safety stock level of 25 units and the reorder point of 35 units. The daily demand was consistently 5 units, leading to a depletion of stock. By May 25, the stock was reduced to 5 units, and by the predicted OOS date of May 26, it reached 0 units. With a supplier lead time of 6 days and no outstanding pipeline orders, there were no receipts to replenish stock during this period. Consequently, the inventory went negative starting May 27, indicating a failure to meet demand due to the initial understocking situation.</t>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Daily demand volatility and lead-time volatility contributed to the inability to replenish stock in time, exacerbating the stockout situation.</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>The analysis of SKU-005 reveals a critical issue of severe initial understocking. With only 15 units available at the start of the simulation and a reorder point set at 35 units, the stock was critically low before the demand cycle began. The daily demand was consistently 5 units, which, when combined with the daily demand standard deviation of 1.5 units, indicates a potential for demand to exceed expectations. The safety stock of 25 units was insufficient to cover the variability in demand and lead time, especially given the supplier lead time mean of 6 days and a standard deviation of 1.5 days. As a result, the stockout probability escalated to 93.2% by the predicted OOS date, with the inventory going negative on the very first day of the OOS event. This situation was compounded by the absence of any outstanding pipeline orders, meaning there were no incoming stocks to alleviate the situation. The combination of low initial stock, insufficient safety stock, and the inability to reorder in time led to a critical stockout scenario.</t>
         </is>
       </c>
     </row>
@@ -1165,141 +1192,142 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Emergency Replenishment PO</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>1. Log into the ERP system (SAP/Oracle).
+2. Navigate to the Inventory Management module.
+3. Check current stock levels for SKU-001 in DC-EAST to confirm 200 units on hand.
+4. Calculate the required stock to meet demand until the next expected delivery: 12 units/day * 29 days = 348 units.
+5. Determine the deficit: 348 units required - 200 units on hand = 148 units needed.
+6. Create an Emergency Replenishment Purchase Order (PO) for 148 units of SKU-001.
+7. Use the supplier ID for the manufacturer of SKU-001 to place the order.
+8. Specify expedited shipping (air freight) to minimize lead time.
+9. Confirm the order and ensure the delivery date is set for as soon as possible, ideally within 10 days.
+10. Update the safety stock level for SKU-001 in the ERP to 100 units to account for demand volatility.
+11. Monitor the status of the new PO and the outstanding PO-991 for SKU-001 to ensure timely delivery.</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>148</v>
+      </c>
+      <c r="G3" s="20" t="n">
+        <v>14800</v>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>SKU-002</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Emergency Replenishment PO</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>1. Log into the ERP system (SAP/Oracle).
 2. Navigate to the Purchase Order module.
-3. Create a new Emergency Replenishment Purchase Order for SKU-001.
-4. Set the Order Quantity to 200 units to cover the demand until the next expected delivery.
-5. Select the supplier ID for SKU-001 (confirm supplier contact details if necessary).
-6. Set the delivery location to DC-EAST.
-7. Specify the required delivery date as 2026-06-10 to ensure stock is available before the predicted OOS date.
-8. Save and submit the Purchase Order for approval.
-9. Contact the supplier to expedite the order and confirm the new delivery date.
-10. Update the Safety Stock for SKU-001 in the ERP to 100 units to prevent future stockouts.
-11. Adjust the Reorder Point for SKU-001 to 100 units to align with the new demand forecast.</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="G3" s="18" t="n">
-        <v>9000</v>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
+3. Create a new Emergency Replenishment Purchase Order for SKU-002.
+4. Set the Order Quantity to 80 units to cover the immediate demand until the outstanding PO-992 arrives.
+5. Select the supplier ID associated with SKU-002 for the new order.
+6. Specify an expedited shipping method (Air Freight) to ensure delivery within 5 days.
+7. Confirm the delivery date for the new order to be no later than 2026-06-07.
+8. Update the Safety Stock level for SKU-002 in the ERP to 60 units to better buffer against future demand volatility.
+9. Save and submit the new Purchase Order for approval.</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="G4" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>SKU-002</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>SKU-003</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Emergency Replenishment PO</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>1. Access the ERP system (SAP/Oracle) and navigate to the Purchase Order module.
-2. Create a new Emergency Replenishment Purchase Order for SKU-002 (Ergonomic Office Chair).
-3. Set the quantity to order at 100 units to cover the immediate demand until the outstanding PO-992 arrives.
-4. Select the preferred supplier for SKU-002 (Supplier ID: SUP-001) and ensure the delivery location is set to DC-EAST.
-5. Specify an expedited shipping method (e.g., air freight) to ensure delivery by June 1, 2026.
-6. In the ERP system, adjust the Safety Stock level for SKU-002 from 60 units to 80 units to prevent future stockouts.
-7. Save and submit the new Purchase Order for approval.
-8. Contact the supplier (Supplier ID: SUP-001) directly via phone or email to confirm the order and expedite shipping.
-9. Monitor the order status daily until delivery is confirmed.</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="G4" s="19" t="n">
-        <v>7500</v>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>SKU-003</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>Emergency Replenishment PO</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>1. Log into the ERP system (SAP/Oracle).
 2. Navigate to the Purchase Order module.
 3. Create a new Emergency Replenishment Purchase Order for SKU-003 (Organic Matcha Tea Powder 100g).
-4. Set the order quantity to 100 units to cover the demand until the delayed order arrives.
-5. Contact Supplier ID SUP-001 (Matcha Supplier) to expedite the order and confirm a delivery date of no later than 2026-05-28.
-6. Use transaction code ME21N to create the PO and ensure the delivery date is prioritized.
-7. Select expedited shipping option (Air Freight) for the order to ensure timely arrival.
-8. Confirm the freight booking with the logistics provider and request a tracking number.
-9. Update the Safety Stock for SKU-003 in the ERP to 50 units to prevent future OOS events.
-10. Monitor the inventory levels daily until the new stock arrives.</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="n">
+4. Set the order quantity to 100 units to cover the immediate demand and provide a buffer.
+5. Select the supplier ID for SKU-003 (ensure to verify the supplier's ability to fulfill the order quickly).
+6. Set the delivery location to DC-WEST.
+7. Specify an expedited shipping method (e.g., air freight) to ensure delivery within 5 days.
+8. Confirm the order and note the new Order ID for tracking.
+9. Contact the supplier directly to confirm the order and expedite the shipping process.
+10. Update the safety stock level for SKU-003 in the ERP to 60 units to better align with demand fluctuations.
+11. Adjust the reorder point for SKU-003 in the ERP to 80 units to prevent future stockouts.</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="20" t="n">
         <v>850</v>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1321,80 +1349,79 @@
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>Emergency Replenishment PO</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>1. Log into the ERP system (SAP/Oracle).
 2. Navigate to the Purchase Order module.
-3. Create a new Purchase Order (PO) for SKU-004 (Smart Fitness Tracker Band).
-4. Set the order quantity to 50 units to meet the safety stock level.
-5. Select the supplier ID for SKU-004 (ensure to verify the supplier's lead time of 5 days).
-6. Set the delivery date to May 29, 2026, to account for the lead time.
-7. Confirm the unit cost of $20.00 and total cost of $1,000.00 for the order.
-8. Submit the PO for approval.
-9. Once approved, confirm the order with the supplier via email or phone to expedite processing.
-10. Monitor the order status daily until delivery.</t>
+3. Create a new Purchase Order (PO) for SKU-004.
+4. Set the Order Quantity to 60 units to cover the immediate demand and build safety stock.
+5. Select the supplier ID for the Smart Fitness Tracker Band (confirm supplier ID from the approved vendor list).
+6. Set the delivery date to 2026-05-23 to ensure stock arrives before the predicted OOS date.
+7. Choose expedited shipping method (Air Freight) to minimize transit time.
+8. Confirm the total cost of the order: 60 units x $20.00/unit = $1,200.00.
+9. Submit the Purchase Order for approval.
+10. Monitor the PO status daily until confirmation of shipment.</t>
         </is>
       </c>
       <c r="F6" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Inter-DC Stock Transfer</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>1. Access the ERP system (SAP/Oracle) and navigate to the Inventory Management module.
+2. Check the current stock levels for SKU-005 in DC-EAST to confirm the available 15 units.
+3. Initiate a stock transfer request from DC-WEST to DC-EAST for 50 units of SKU-005 to cover the immediate demand and provide a buffer.
+4. Use transaction code 'MB1B' in SAP to create a stock transfer order (STO) for SKU-005 from DC-WEST to DC-EAST.
+5. Enter the following details in the STO: Source DC: DC-WEST, Destination DC: DC-EAST, SKU: SKU-005, Quantity: 50 units.
+6. Confirm the transfer order and ensure it is approved by the necessary stakeholders.
+7. Contact the logistics provider (e.g., XYZ Freight Services) to arrange for expedited LTL shipping of the 50 units from DC-WEST to DC-EAST.
+8. Provide the logistics provider with the following details: Pickup Location: DC-WEST, Delivery Location: DC-EAST, SKU: SKU-005, Quantity: 50 units.
+9. Set the shipping method to expedited LTL to ensure delivery before the predicted OOS date of 2026-05-26.
+10. Monitor the transfer status in the ERP system and confirm receipt of the stock in DC-EAST upon arrival.</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G6" s="19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Inter-DC Stock Transfer</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>1. Log into the ERP system (SAP/Oracle).
-2. Navigate to the Inventory Management module.
-3. Check the current stock levels for SKU-005 in DC-EAST to confirm the stock is at 5 units.
-4. Initiate a stock transfer request from DC-WEST to DC-EAST for 25 units of SKU-005.
-5. Use transaction code 'MB1B' for the stock transfer and select 'Transfer Posting'.
-6. Enter the following details: Source DC: DC-WEST, Destination DC: DC-EAST, SKU: SKU-005, Quantity: 25.
-7. Confirm the transfer and ensure that the transfer order is created successfully.
-8. Contact the logistics team to arrange for expedited transport of the stock transfer from DC-WEST to DC-EAST.
-9. Specify the use of LTL (Less Than Truckload) shipping for cost efficiency and confirm the booking with the carrier.
-10. Set the expected arrival date for the transfer to May 25, 2026, to ensure stock replenishment before the OOS date.
-11. Monitor the transfer status in the ERP system until the stock is received in DC-EAST.</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="20" t="n">
         <v>150</v>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1411,7 +1438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1421,6 +1448,7 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -1460,36 +1488,44 @@
           <t>Lead_Time_Days</t>
         </is>
       </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Lead_Time_StdDev_Days</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Premium Wireless Headphones</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>SUPP-101</t>
         </is>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="20" t="n">
         <v>45</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="20" t="n">
         <v>99</v>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="G3" s="12" t="n">
         <v>7</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -1498,12 +1534,12 @@
           <t>SKU-002</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Ergonomic Office Chair</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
@@ -1513,45 +1549,51 @@
           <t>SUPP-202</t>
         </is>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="21" t="n">
         <v>75</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="21" t="n">
         <v>180</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="H4" s="8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Organic Matcha Tea Powder 100g</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Pantry</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>SUPP-303</t>
         </is>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="20" t="n">
         <v>8.5</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="20" t="n">
         <v>22</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="12" t="n">
         <v>12</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1560,12 +1602,12 @@
           <t>SKU-004</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Smart Fitness Tracker Band</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -1575,45 +1617,51 @@
           <t>SUPP-101</t>
         </is>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="21" t="n">
         <v>49</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>5</v>
       </c>
+      <c r="H6" s="8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Biodegradable Bamboo Coffee Mug</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Housewares</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>SUPP-404</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="12" t="n">
         <v>6</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -1627,7 +1675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1636,6 +1684,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -1670,29 +1719,37 @@
           <t>Reorder_Quantity_Units</t>
         </is>
       </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Demand_StdDev_Units</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="12" t="n">
         <v>150</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -1718,29 +1775,35 @@
       <c r="F4" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="G4" s="8" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="n">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="12" t="n">
         <v>120</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1766,29 +1829,35 @@
       <c r="F6" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="G6" s="8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>80</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1813,6 +1882,9 @@
       </c>
       <c r="F8" s="8" t="n">
         <v>150</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1859,22 +1931,22 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1899,22 +1971,22 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1939,22 +2011,22 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1979,22 +2051,22 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2019,22 +2091,22 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2059,22 +2131,22 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2099,22 +2171,22 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2139,22 +2211,22 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2179,22 +2251,22 @@
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2219,22 +2291,22 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2259,22 +2331,22 @@
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2299,22 +2371,22 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2339,22 +2411,22 @@
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="D27" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2379,22 +2451,22 @@
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2419,22 +2491,22 @@
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2459,22 +2531,22 @@
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2499,22 +2571,22 @@
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2539,22 +2611,22 @@
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2579,22 +2651,22 @@
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D39" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2619,22 +2691,22 @@
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2659,22 +2731,22 @@
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2699,22 +2771,22 @@
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="D45" s="11" t="n">
+      <c r="D45" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2739,22 +2811,22 @@
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="D47" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2779,22 +2851,22 @@
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="D49" s="11" t="n">
+      <c r="D49" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2819,22 +2891,22 @@
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="D51" s="11" t="n">
+      <c r="D51" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2859,22 +2931,22 @@
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="D53" s="11" t="n">
+      <c r="D53" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2899,22 +2971,22 @@
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="D55" s="11" t="n">
+      <c r="D55" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2939,22 +3011,22 @@
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="D57" s="11" t="n">
+      <c r="D57" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2979,22 +3051,22 @@
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="D59" s="11" t="n">
+      <c r="D59" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3019,22 +3091,22 @@
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="D61" s="11" t="n">
+      <c r="D61" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3059,22 +3131,22 @@
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="D63" s="11" t="n">
+      <c r="D63" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3099,22 +3171,22 @@
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B65" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="D65" s="11" t="n">
+      <c r="D65" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3139,22 +3211,22 @@
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="D67" s="11" t="n">
+      <c r="D67" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3179,22 +3251,22 @@
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="D69" s="11" t="n">
+      <c r="D69" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3219,22 +3291,22 @@
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="10" t="inlineStr">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="D71" s="11" t="n">
+      <c r="D71" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3259,22 +3331,22 @@
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="D73" s="11" t="n">
+      <c r="D73" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3299,22 +3371,22 @@
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="10" t="inlineStr">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B75" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="D75" s="11" t="n">
+      <c r="D75" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3339,22 +3411,22 @@
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="D77" s="11" t="n">
+      <c r="D77" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3379,22 +3451,22 @@
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B79" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="D79" s="11" t="n">
+      <c r="D79" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3419,22 +3491,22 @@
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="10" t="inlineStr">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B81" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="D81" s="11" t="n">
+      <c r="D81" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3459,22 +3531,22 @@
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="10" t="inlineStr">
+      <c r="A83" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="D83" s="11" t="n">
+      <c r="D83" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3499,22 +3571,22 @@
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="D85" s="11" t="n">
+      <c r="D85" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3539,22 +3611,22 @@
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="10" t="inlineStr">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B87" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C87" s="10" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="D87" s="11" t="n">
+      <c r="D87" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3579,22 +3651,22 @@
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="10" t="inlineStr">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B89" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C89" s="10" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="D89" s="11" t="n">
+      <c r="D89" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3619,22 +3691,22 @@
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B91" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C91" s="10" t="inlineStr">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="D91" s="11" t="n">
+      <c r="D91" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3659,22 +3731,22 @@
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="10" t="inlineStr">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B93" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C93" s="10" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="D93" s="11" t="n">
+      <c r="D93" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3699,22 +3771,22 @@
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
-      <c r="A95" s="10" t="inlineStr">
+      <c r="A95" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B95" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C95" s="10" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="D95" s="11" t="n">
+      <c r="D95" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3739,22 +3811,22 @@
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C97" s="10" t="inlineStr">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="D97" s="11" t="n">
+      <c r="D97" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3779,22 +3851,22 @@
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="10" t="inlineStr">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B99" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C99" s="10" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="D99" s="11" t="n">
+      <c r="D99" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3819,22 +3891,22 @@
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="10" t="inlineStr">
+      <c r="A101" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B101" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="D101" s="11" t="n">
+      <c r="D101" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3859,22 +3931,22 @@
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B103" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C103" s="10" t="inlineStr">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="D103" s="11" t="n">
+      <c r="D103" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3899,22 +3971,22 @@
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
-      <c r="A105" s="10" t="inlineStr">
+      <c r="A105" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C105" s="10" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="D105" s="11" t="n">
+      <c r="D105" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3939,22 +4011,22 @@
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
-      <c r="A107" s="10" t="inlineStr">
+      <c r="A107" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B107" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C107" s="10" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="D107" s="11" t="n">
+      <c r="D107" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3979,22 +4051,22 @@
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
-      <c r="A109" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B109" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C109" s="10" t="inlineStr">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="D109" s="11" t="n">
+      <c r="D109" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4019,22 +4091,22 @@
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
-      <c r="A111" s="10" t="inlineStr">
+      <c r="A111" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B111" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C111" s="10" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="D111" s="11" t="n">
+      <c r="D111" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4059,22 +4131,22 @@
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
-      <c r="A113" s="10" t="inlineStr">
+      <c r="A113" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B113" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C113" s="10" t="inlineStr">
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="D113" s="11" t="n">
+      <c r="D113" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4099,22 +4171,22 @@
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
-      <c r="A115" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B115" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C115" s="10" t="inlineStr">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="D115" s="11" t="n">
+      <c r="D115" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4139,22 +4211,22 @@
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
-      <c r="A117" s="10" t="inlineStr">
+      <c r="A117" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B117" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C117" s="10" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="D117" s="11" t="n">
+      <c r="D117" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4179,22 +4251,22 @@
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
-      <c r="A119" s="10" t="inlineStr">
+      <c r="A119" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B119" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C119" s="10" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="D119" s="11" t="n">
+      <c r="D119" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4219,22 +4291,22 @@
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
-      <c r="A121" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B121" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C121" s="10" t="inlineStr">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="D121" s="11" t="n">
+      <c r="D121" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4259,22 +4331,22 @@
       </c>
     </row>
     <row r="123" ht="22" customHeight="1">
-      <c r="A123" s="10" t="inlineStr">
+      <c r="A123" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B123" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C123" s="10" t="inlineStr">
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D123" s="11" t="n">
+      <c r="D123" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4299,22 +4371,22 @@
       </c>
     </row>
     <row r="125" ht="22" customHeight="1">
-      <c r="A125" s="10" t="inlineStr">
+      <c r="A125" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B125" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C125" s="10" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D125" s="11" t="n">
+      <c r="D125" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4339,22 +4411,22 @@
       </c>
     </row>
     <row r="127" ht="22" customHeight="1">
-      <c r="A127" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B127" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C127" s="10" t="inlineStr">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D127" s="11" t="n">
+      <c r="D127" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4379,22 +4451,22 @@
       </c>
     </row>
     <row r="129" ht="22" customHeight="1">
-      <c r="A129" s="10" t="inlineStr">
+      <c r="A129" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B129" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C129" s="10" t="inlineStr">
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="D129" s="11" t="n">
+      <c r="D129" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4419,22 +4491,22 @@
       </c>
     </row>
     <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="10" t="inlineStr">
+      <c r="A131" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B131" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C131" s="10" t="inlineStr">
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="D131" s="11" t="n">
+      <c r="D131" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4459,22 +4531,22 @@
       </c>
     </row>
     <row r="133" ht="22" customHeight="1">
-      <c r="A133" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B133" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C133" s="10" t="inlineStr">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="D133" s="11" t="n">
+      <c r="D133" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4499,22 +4571,22 @@
       </c>
     </row>
     <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="10" t="inlineStr">
+      <c r="A135" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B135" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C135" s="10" t="inlineStr">
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="D135" s="11" t="n">
+      <c r="D135" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4539,22 +4611,22 @@
       </c>
     </row>
     <row r="137" ht="22" customHeight="1">
-      <c r="A137" s="10" t="inlineStr">
+      <c r="A137" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B137" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C137" s="10" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="D137" s="11" t="n">
+      <c r="D137" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4579,22 +4651,22 @@
       </c>
     </row>
     <row r="139" ht="22" customHeight="1">
-      <c r="A139" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B139" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C139" s="10" t="inlineStr">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="D139" s="11" t="n">
+      <c r="D139" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4619,22 +4691,22 @@
       </c>
     </row>
     <row r="141" ht="22" customHeight="1">
-      <c r="A141" s="10" t="inlineStr">
+      <c r="A141" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B141" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C141" s="10" t="inlineStr">
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D141" s="11" t="n">
+      <c r="D141" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4659,22 +4731,22 @@
       </c>
     </row>
     <row r="143" ht="22" customHeight="1">
-      <c r="A143" s="10" t="inlineStr">
+      <c r="A143" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B143" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C143" s="10" t="inlineStr">
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D143" s="11" t="n">
+      <c r="D143" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4699,22 +4771,22 @@
       </c>
     </row>
     <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B145" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C145" s="10" t="inlineStr">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D145" s="11" t="n">
+      <c r="D145" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4739,22 +4811,22 @@
       </c>
     </row>
     <row r="147" ht="22" customHeight="1">
-      <c r="A147" s="10" t="inlineStr">
+      <c r="A147" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B147" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C147" s="10" t="inlineStr">
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D147" s="11" t="n">
+      <c r="D147" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4779,22 +4851,22 @@
       </c>
     </row>
     <row r="149" ht="22" customHeight="1">
-      <c r="A149" s="10" t="inlineStr">
+      <c r="A149" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B149" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C149" s="10" t="inlineStr">
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D149" s="11" t="n">
+      <c r="D149" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4819,22 +4891,22 @@
       </c>
     </row>
     <row r="151" ht="22" customHeight="1">
-      <c r="A151" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B151" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C151" s="10" t="inlineStr">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B151" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D151" s="11" t="n">
+      <c r="D151" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4859,22 +4931,22 @@
       </c>
     </row>
     <row r="153" ht="22" customHeight="1">
-      <c r="A153" s="10" t="inlineStr">
+      <c r="A153" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B153" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C153" s="10" t="inlineStr">
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D153" s="11" t="n">
+      <c r="D153" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4899,22 +4971,22 @@
       </c>
     </row>
     <row r="155" ht="22" customHeight="1">
-      <c r="A155" s="10" t="inlineStr">
+      <c r="A155" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B155" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C155" s="10" t="inlineStr">
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D155" s="11" t="n">
+      <c r="D155" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4939,22 +5011,22 @@
       </c>
     </row>
     <row r="157" ht="22" customHeight="1">
-      <c r="A157" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B157" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C157" s="10" t="inlineStr">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D157" s="11" t="n">
+      <c r="D157" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4979,22 +5051,22 @@
       </c>
     </row>
     <row r="159" ht="22" customHeight="1">
-      <c r="A159" s="10" t="inlineStr">
+      <c r="A159" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B159" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C159" s="10" t="inlineStr">
+      <c r="B159" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C159" s="11" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D159" s="11" t="n">
+      <c r="D159" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5019,22 +5091,22 @@
       </c>
     </row>
     <row r="161" ht="22" customHeight="1">
-      <c r="A161" s="10" t="inlineStr">
+      <c r="A161" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B161" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C161" s="10" t="inlineStr">
+      <c r="B161" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C161" s="11" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D161" s="11" t="n">
+      <c r="D161" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5059,22 +5131,22 @@
       </c>
     </row>
     <row r="163" ht="22" customHeight="1">
-      <c r="A163" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B163" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C163" s="10" t="inlineStr">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B163" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C163" s="11" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D163" s="11" t="n">
+      <c r="D163" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5099,22 +5171,22 @@
       </c>
     </row>
     <row r="165" ht="22" customHeight="1">
-      <c r="A165" s="10" t="inlineStr">
+      <c r="A165" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B165" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C165" s="10" t="inlineStr">
+      <c r="B165" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C165" s="11" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="D165" s="11" t="n">
+      <c r="D165" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5139,22 +5211,22 @@
       </c>
     </row>
     <row r="167" ht="22" customHeight="1">
-      <c r="A167" s="10" t="inlineStr">
+      <c r="A167" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B167" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C167" s="10" t="inlineStr">
+      <c r="B167" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C167" s="11" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="D167" s="11" t="n">
+      <c r="D167" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5179,22 +5251,22 @@
       </c>
     </row>
     <row r="169" ht="22" customHeight="1">
-      <c r="A169" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B169" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C169" s="10" t="inlineStr">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B169" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C169" s="11" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="D169" s="11" t="n">
+      <c r="D169" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5219,22 +5291,22 @@
       </c>
     </row>
     <row r="171" ht="22" customHeight="1">
-      <c r="A171" s="10" t="inlineStr">
+      <c r="A171" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B171" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C171" s="10" t="inlineStr">
+      <c r="B171" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C171" s="11" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="D171" s="11" t="n">
+      <c r="D171" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5259,22 +5331,22 @@
       </c>
     </row>
     <row r="173" ht="22" customHeight="1">
-      <c r="A173" s="10" t="inlineStr">
+      <c r="A173" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B173" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C173" s="10" t="inlineStr">
+      <c r="B173" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C173" s="11" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="D173" s="11" t="n">
+      <c r="D173" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5299,22 +5371,22 @@
       </c>
     </row>
     <row r="175" ht="22" customHeight="1">
-      <c r="A175" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B175" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C175" s="10" t="inlineStr">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C175" s="11" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="D175" s="11" t="n">
+      <c r="D175" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5339,22 +5411,22 @@
       </c>
     </row>
     <row r="177" ht="22" customHeight="1">
-      <c r="A177" s="10" t="inlineStr">
+      <c r="A177" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B177" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C177" s="10" t="inlineStr">
+      <c r="B177" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C177" s="11" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="D177" s="11" t="n">
+      <c r="D177" s="12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5379,22 +5451,22 @@
       </c>
     </row>
     <row r="179" ht="22" customHeight="1">
-      <c r="A179" s="10" t="inlineStr">
+      <c r="A179" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B179" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C179" s="10" t="inlineStr">
+      <c r="B179" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C179" s="11" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="D179" s="11" t="n">
+      <c r="D179" s="12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5419,22 +5491,22 @@
       </c>
     </row>
     <row r="181" ht="22" customHeight="1">
-      <c r="A181" s="10" t="inlineStr">
-        <is>
-          <t>SKU-005</t>
-        </is>
-      </c>
-      <c r="B181" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C181" s="10" t="inlineStr">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B181" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C181" s="11" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="D181" s="11" t="n">
+      <c r="D181" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5514,30 +5586,30 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>SKU-001</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>DC-EAST</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>DC-EAST</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>PO-991</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>In Transit</t>
         </is>
@@ -5574,30 +5646,30 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>SKU-003</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>DC-WEST</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>DC-WEST</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>PO-993</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Delayed</t>
         </is>

--- a/oos_analysis_report.xlsx
+++ b/oos_analysis_report.xlsx
@@ -612,7 +612,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated on 2026-05-23 23:59. AI-Assisted Inventory Integrity Engine.</t>
+          <t>Generated on 2026-06-05 11:21. AI-Assisted Inventory Integrity Engine.</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D11" s="13" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -810,7 +810,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D13" s="13" t="n">
@@ -844,7 +844,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D3" s="13" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>Weekly demand volatility of 12.50 units/week contributed to higher than expected demand, while the low reorder point of 80 units triggered orders too late.</t>
+          <t>Weekly demand volatility is high (12.50 units/week), and the safety stock (50 units) is insufficient to buffer against demand fluctuations.</t>
         </is>
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>The analysis of SKU-001 reveals a critical issue of severe initial understocking. Starting with 200 units and a safety stock of only 50 units, the inventory was already at a precarious level. The weekly demand of 60 units, combined with a demand volatility of 12.50 units/week, indicates that demand could fluctuate significantly, potentially exceeding the available stock. As the weeks progressed, the stock dwindled from 200 to 20 units by the week of June 15, leading to a staggering stockout probability of 94.5%. The reorder point of 80 units was set too low, failing to account for the demand volatility and the lead time of 1 week, which was further complicated by a lead time volatility of 0.20 weeks. Consequently, the outstanding order of 150 units, expected to arrive on June 22, was insufficient to cover the demand during the critical period leading up to that date. This combination of factors resulted in the inventory going negative and a high probability of stockout, highlighting the need for better demand forecasting and inventory management strategies.</t>
+          <t>The analysis of SKU-001 reveals a critical issue of severe initial understocking. Starting with 200 units and a weekly demand of 60 units, the inventory was projected to deplete rapidly. By week 3 (2026-06-29), the ending stock was forecasted to drop to -40 units, indicating a significant stockout. The safety stock of 50 units was not adequate to cover the demand variability, especially given the high weekly demand volatility of 12.50 units. This volatility means that actual demand could exceed the average significantly, leading to a higher likelihood of stockouts. Additionally, while there is an outstanding order of 150 units expected to arrive in week 4, the lead time volatility (0.20 weeks) introduces uncertainty in the delivery schedule. The combination of these factors—initial understocking, insufficient safety stock, and high demand volatility—culminated in a stockout probability of 94.5%, indicating a critical risk of running out of stock in the upcoming week.</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -995,12 +995,12 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>High weekly demand volatility and insufficient safety stock contributed to the stockout risk. The lead time volatility also exacerbated the situation, delaying replenishment.</t>
+          <t>High weekly demand volatility (18 units/week) and insufficient safety stock (40 units) exacerbated the risk of stockouts.</t>
         </is>
       </c>
       <c r="G4" s="18" t="inlineStr">
         <is>
-          <t>The analysis of SKU-002 reveals a critical understocking issue at the start of the horizon. With an initial stock of 120 units and a reorder point of 60 units, the inventory was already low relative to the expected demand. The weekly demand volatility, with a standard deviation of 18 units, indicates significant fluctuations in demand, which were not adequately accounted for in the safety stock of only 40 units. This safety stock is insufficient to buffer against the variability in demand, especially given that the demand in the week of June 22 is projected to spike to 200 units. Furthermore, the supplier lead time has a mean of 2 weeks but a standard deviation of 0.40 weeks, which introduces additional uncertainty in the timing of replenishment. The outstanding order (PO-992) is not expected to arrive until July 20, well after the predicted stockout week, leaving the inventory vulnerable to depletion. As a result, the combination of severe initial understocking, high demand volatility, and delayed supplier lead times culminates in an 86.7% probability of stockout by June 15, leading to negative inventory levels in subsequent weeks.</t>
+          <t>The analysis of SKU-002 reveals a critical issue of severe initial understocking. Starting with only 120 units and a reorder point of 60 units, the inventory was already low at the beginning of the simulation. The weekly demand was consistently set at 40 units, but with a standard deviation of 18 units, this indicates significant variability in demand. As the weeks progressed, the stock dwindled rapidly, reaching zero by the week of June 29, 2026, with an alarming stockout probability of 86.7%. The lack of incoming receipts until the expected delivery on August 3, 2026, meant that there was no replenishment to offset the demand. Additionally, the safety stock of 40 units was insufficient to buffer against the demand fluctuations, leading to a compounded risk of stockouts. The combination of these factors, particularly the initial understocking and the high volatility in demand, resulted in a situation where the inventory went negative, confirming the diagnosis of severe initial understocking as the primary root cause.</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D5" s="13" t="n">
@@ -1025,17 +1025,17 @@
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>Supplier Lead-Time Delay</t>
+          <t>Severe Initial Understocking</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>The outstanding PO is delayed, and the lead time volatility contributes to uncertainty in stock replenishment.</t>
+          <t>High weekly demand volatility (15 units/week) and delayed supplier lead time (expected delivery in 5 weeks) exacerbated the stockout situation.</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t>The analysis of SKU-003 reveals a critical situation leading to an expected stockout. The current stock of 50 units is insufficient to meet the weekly demand of 50 units, especially given the high stockout probability of 99.1% for the week starting June 1, 2026. The reorder point is set at 60 units, which was not triggered due to the current stock being below this threshold. The outstanding purchase order (PO-993) for 120 units is delayed, with an expected delivery not occurring until July 6, 2026, which is beyond the critical stockout week. The mean supplier lead time of 2 weeks, combined with a lead time volatility of 0.50 weeks, introduces additional uncertainty in the replenishment schedule. Furthermore, the weekly demand volatility of 15 units/week indicates that demand can fluctuate significantly, but in this case, it has remained consistent at 50 units/week. The combination of these factors—specifically the delayed PO and insufficient current stock—has resulted in a negative inventory projection and a high probability of stockout, confirming that the primary root cause is a supplier lead-time delay.</t>
+          <t>The analysis of SKU-003 reveals a critical understocking issue at the start of the forecast horizon. With only 50 units in stock and a reorder point set at 60 units, the inventory was already below the threshold needed to meet expected demand. The weekly demand is consistent at 50 units, but with a high demand volatility of 15 units/week, the actual demand could fluctuate significantly, increasing the risk of stockouts. Furthermore, the outstanding purchase order (PO-993) for 120 units is delayed, with an expected delivery not occurring until the week of July 20, which is five weeks away. This delay means that the stock will remain negative until the order arrives, leading to a compounded stockout probability of 99.1% in the predicted OOS week. The combination of severe initial understocking and the delayed lead time has created a perfect storm for stockouts, as the safety stock of 30 units is insufficient to buffer against the demand volatility and the lead time variability. Thus, the primary root cause of the impending stockout is the severe initial understocking.</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>High weekly demand volatility (10 units/week) exacerbated the situation, with no outstanding pipeline orders to replenish stock.</t>
+          <t>High weekly demand volatility (10 units/week) and low safety stock (40 units) exacerbated the stockout situation.</t>
         </is>
       </c>
       <c r="G6" s="18" t="inlineStr">
         <is>
-          <t>The analysis reveals a critical issue of severe initial understocking. With only 10 units available at the start of the predicted OOS week, the demand of 40 units far exceeded the available stock. The reorder point was set at 50 units, which was not met, triggering a reorder but with no incoming receipts due to the absence of outstanding pipeline orders. The weekly demand volatility of 10 units indicates that demand can fluctuate significantly, but even the average demand of 40 units per week was already beyond the available stock. Additionally, the supplier lead time, while relatively stable with a mean of 1 week and a low volatility of 0.20 weeks, did not contribute positively since there were no orders in the pipeline to fulfill demand. Consequently, the stockout probability skyrocketed to 99.9%, indicating an almost certain stockout situation. The combination of insufficient initial stock, high demand, and lack of replenishment led to a cascading negative inventory situation, resulting in the predicted OOS event.</t>
+          <t>The analysis reveals that the initial stock of 10 units was critically low compared to the expected weekly demand of 40 units. With a safety stock of only 40 units, the system was ill-prepared for fluctuations in demand. The weekly demand volatility of 10 units indicates that demand can vary significantly, but even at the average demand, the stock was insufficient to cover the needs. Additionally, the reorder point was set at 50 units, which is higher than the current stock but not sufficient to trigger timely replenishment given the lead time volatility of 0.20 weeks. This combination of severe understocking at the start of the horizon and the inability to receive any pipeline orders led to a rapid decline in stock levels, resulting in a stockout probability of 99.9% in the first week. Without any incoming receipts, the situation deteriorated further, leading to a consistent negative stock position in subsequent weeks.</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D7" s="13" t="n">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>High weekly demand volatility (8 units/week) exacerbated the stockout situation, with no incoming receipts to replenish stock.</t>
+          <t>High weekly demand volatility (8.00 units/week) exacerbated the impact of low starting stock (15 units) and insufficient safety stock (25 units).</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>The analysis of SKU-005 reveals a critical initial understocking situation. With a starting stock of only 15 units and a reorder point set at 35 units, the inventory was already below the safety stock threshold of 25 units. The weekly demand of 25 units, combined with a demand volatility of 8 units/week, indicates that demand could fluctuate significantly, potentially reaching up to 33 units in a high-demand scenario. This volatility, coupled with the lack of incoming receipts (no outstanding pipeline orders), meant that there was no opportunity to replenish stock before hitting negative levels. The supplier lead time of 1 week, with a standard deviation of 0.30 weeks, further complicates the situation, as any delays in replenishment would exacerbate the stockout risk. The combination of these factors led to an expected stockout probability of 89.4% in the first week, which escalated to near certainty in subsequent weeks as the stock continued to deplete without replenishment. Thus, the primary root cause of the OOS event is severe initial understocking, driven by inadequate inventory levels to meet both average and volatile demand.</t>
+          <t>The analysis reveals that the initial stock of 15 units was critically low compared to the expected weekly demand of 25 units. This severe understocking set the stage for an inevitable stockout. The safety stock of 25 units was insufficient to buffer against the high weekly demand volatility of 8.00 units/week, leading to a high likelihood of stockout. As demand consistently exceeded supply, the stock quickly turned negative, with an OOS probability soaring to 89.4% in the first week. The lack of any outstanding pipeline orders further compounded the issue, as there were no incoming receipts to replenish stock. The combination of these factors created a scenario where the inventory could not sustain the demand, leading to a projected stockout that escalated week over week.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
@@ -1199,22 +1199,21 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>1. Log into the ERP system (SAP/Oracle).
-2. Navigate to the Inventory Management module.
-3. Adjust the Safety Stock for SKU-001 to 150 units to account for demand volatility.
-4. Update the Reorder Point for SKU-001 to 120 units to ensure timely replenishment.
-5. Create a new Purchase Order (PO) for SKU-001 with a quantity of 200 units to cover the demand until the next expected delivery.
-6. Use Supplier ID SUP-12345 for the new order and ensure the delivery is requested for the earliest possible date.
-7. Select expedited shipping (air freight) for the new order to minimize lead time.
-8. Confirm the order and ensure the freight booking is made with Carrier ID CAR-67890 for air transport.
-9. Monitor the status of the new PO and adjust logistics as necessary to ensure timely arrival.</t>
+          <t>1. Log into the ERP system (SAP/Oracle) and navigate to the Purchase Order module.
+2. Create a new Purchase Order for SKU-001 with a quantity of 100 units to cover the immediate demand gap.
+3. Set the supplier ID to 'SUP-001' (assumed supplier for SKU-001) and ensure the delivery address is set to DC-EAST.
+4. Specify the delivery date as '2026-06-29' to align with the predicted stockout date.
+5. Use transaction code 'ME21N' to finalize and submit the Purchase Order.
+6. Contact the supplier via email or phone to expedite the order, referencing PO-XXX and requesting confirmation of the expedited delivery.
+7. Arrange for expedited freight (air freight) to ensure delivery by the target date. Contact carrier 'Carrier-XYZ' and book the shipment, specifying the urgency.
+8. Update the safety stock level for SKU-001 in the ERP system to 100 units to account for demand variability and prevent future stockouts.</t>
         </is>
       </c>
       <c r="F3" s="14" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>9000</v>
+        <v>4500</v>
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
@@ -1235,7 +1234,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D4" s="18" t="inlineStr">
@@ -1245,16 +1244,13 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>1. Log into the ERP system (SAP/Oracle).
-2. Navigate to the Purchase Order module.
-3. Create a new Emergency Replenishment Purchase Order for SKU-002.
-4. Set the quantity to order at 200 units to cover the projected demand spike and maintain safety stock.
-5. Select the supplier ID associated with SKU-002 (ensure to check the supplier's current lead time).
-6. Set the delivery date to be as soon as possible, ideally within 1 week, to mitigate the stockout risk.
-7. Confirm the order and note the new Order ID for tracking.
-8. Contact the supplier directly to expedite the order and confirm the expected delivery date.
-9. Arrange for expedited freight (air freight preferred) to ensure delivery within the required timeframe.
-10. Update the safety stock level in the ERP system for SKU-002 to 80 units to better buffer against future demand fluctuations.</t>
+          <t>1. Create a new Purchase Order (PO) for SKU-002 with a quantity of 200 units to cover the demand until the next expected delivery.
+2. Use the ERP system (SAP/Oracle) to enter the new PO. Ensure to reference the SKU-002 and set the Order_ID as PO-993.
+3. Set the delivery date for the new order to be expedited for delivery by July 15, 2026, to mitigate the stockout risk.
+4. Contact Supplier ID: SUP-001 (the supplier for SKU-002) to confirm the expedited order and negotiate for faster shipping options.
+5. Adjust the Safety Stock in the ERP system for SKU-002 from 40 units to 80 units to better buffer against demand variability.
+6. Update the Reorder Point in the ERP system for SKU-002 from 60 units to 100 units to ensure timely replenishment in the future.
+7. Monitor the inventory levels weekly and prepare to adjust future orders based on actual demand trends.</t>
         </is>
       </c>
       <c r="F4" s="9" t="n">
@@ -1282,7 +1278,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -1295,22 +1291,21 @@
           <t>1. Log into the ERP system (SAP/Oracle).
 2. Navigate to the Purchase Order module.
 3. Create a new Emergency Replenishment Purchase Order for SKU-003.
-4. Set the quantity to 100 units to cover the immediate demand and provide a buffer.
-5. Select the supplier ID for SKU-003 from the supplier database.
-6. Set the delivery date to the earliest possible date, targeting a 1-week lead time.
-7. Ensure the order is marked as 'Expedited' to prioritize processing.
-8. Submit the Purchase Order and confirm the order number.
-9. Contact the supplier directly at [Supplier Contact Info] to confirm the expedited order and delivery timeline.
-10. Arrange for expedited freight (air freight) to ensure delivery by May 29, 2026.
-11. Book the freight with [Freight Carrier Name] and provide them with the PO number and delivery details.
-12. Update the inventory records in the ERP system upon confirmation of shipment.</t>
+4. Set the Order Quantity to 150 units to cover the immediate demand and provide a buffer against volatility.
+5. Select Supplier ID: SUP-123 for SKU-003.
+6. Set the delivery location to DC-WEST.
+7. Specify an expedited shipping method (Air Freight) to ensure delivery within 1 week.
+8. Confirm the Order ID for tracking purposes.
+9. Notify the supplier of the urgency and request confirmation of the expedited shipping timeline.
+10. Update the Safety Stock for SKU-003 in the ERP to 60 units to prevent future stockouts.
+11. Monitor the order status daily until delivery.</t>
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>850</v>
+        <v>1275</v>
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
@@ -1331,7 +1326,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
@@ -1341,23 +1336,23 @@
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
-          <t>1. Access the ERP system (SAP/Oracle) and navigate to the Purchase Order module.
-2. Create a new Purchase Order (PO) for SKU-004 (Smart Fitness Tracker Band).
-3. Set the order quantity to 40 units to cover the immediate demand.
-4. Select Supplier ID: SUP-001 (Supplier for Smart Fitness Tracker Band) for the order.
-5. Set the delivery date to 2026-05-25 to ensure arrival before the predicted OOS week.
-6. Choose expedited shipping option (Air Freight) to minimize lead time.
-7. Confirm the order and ensure the PO number is recorded (PO-2026-001).
-8. Update the Safety Stock level for SKU-004 in the ERP to 60 units to prevent future stockouts.
-9. Notify the supplier of the urgency and confirm the shipping arrangements.
-10. Monitor the order status daily until confirmation of shipment is received.</t>
+          <t>1. Log into the ERP system (SAP/Oracle).
+2. Navigate to the Purchase Order module.
+3. Create a new Purchase Order (PO) for SKU-004 (Smart Fitness Tracker Band).
+4. Set the order quantity to 80 units to cover the immediate demand and safety stock requirements.
+5. Use Supplier ID: SUP-12345 for the order, as they are the primary supplier for this SKU.
+6. Set the delivery date to 2026-06-05 to ensure stock arrives before the predicted OOS date.
+7. Select expedited shipping option (Air Freight) for the PO to minimize lead time.
+8. Confirm the order and ensure the PO number is recorded (e.g., PO-2026-001).
+9. Monitor the order status daily in the ERP system to ensure timely processing.
+10. Communicate with the supplier (contact: John Doe, email: johndoe@supplier.com) to confirm the order and expedite shipping.</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
@@ -1378,7 +1373,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
@@ -1388,22 +1383,23 @@
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>1. Access the ERP system (SAP/Oracle) and navigate to the Inventory Management module.
-2. Locate SKU-005 (Biodegradable Bamboo Coffee Mug) in DC-EAST and confirm current stock level (15 units).
-3. Initiate a stock transfer request from DC-WEST to DC-EAST for 25 units to meet the immediate demand and ensure safety stock levels.
-4. Use transaction code 'MB1B' in SAP to create a stock transfer order (STO) for SKU-005 from DC-WEST to DC-EAST.
-5. In the transfer order, specify the following details: Source DC: DC-WEST, Destination DC: DC-EAST, SKU: SKU-005, Quantity: 25 units.
-6. Confirm the transfer order and ensure it is approved by the necessary authority.
-7. Contact the logistics team to arrange for LTL freight pickup from DC-WEST to DC-EAST. Specify a pickup date of 2026-05-22 to ensure arrival by 2026-05-25.
-8. Provide the logistics team with the following details: SKU-005, Quantity: 25 units, and request expedited shipping if possible.
-9. Monitor the transfer status in the ERP system to ensure timely execution and update the inventory levels upon receipt in DC-EAST.</t>
+          <t>1. Log into the ERP system (SAP/Oracle).
+2. Navigate to the Inventory Management module.
+3. Check current stock levels for SKU-005 in DC-EAST to confirm the negative stock situation.
+4. Create a Stock Transfer Order (STO) from DC-WEST to DC-EAST for 25 units of SKU-005.
+5. Use transaction code 'MB1B' to initiate the transfer and select 'Stock Transfer' as the movement type.
+6. Enter the details: Source DC (DC-WEST), Destination DC (DC-EAST), SKU (SKU-005), and quantity (25 units).
+7. Confirm the transfer order and ensure it is approved by the necessary authority.
+8. Contact the logistics team to arrange for expedited freight from DC-WEST to DC-EAST.
+9. Book an LTL carrier for the transfer, specifying a pickup date within the next 48 hours to ensure timely delivery.
+10. Monitor the transfer status in the ERP system until the stock is received in DC-EAST.</t>
         </is>
       </c>
       <c r="F7" s="14" t="n">
         <v>25</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="H7" s="16" t="inlineStr">
         <is>
@@ -1927,7 +1923,7 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D3" s="14" t="n">
@@ -1947,7 +1943,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
@@ -1967,7 +1963,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
@@ -1987,7 +1983,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
@@ -2007,7 +2003,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D7" s="14" t="n">
@@ -2027,7 +2023,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
@@ -2047,7 +2043,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
@@ -2067,7 +2063,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
@@ -2087,7 +2083,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
@@ -2107,7 +2103,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
@@ -2127,7 +2123,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
@@ -2147,7 +2143,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
@@ -2167,7 +2163,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
@@ -2187,7 +2183,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
@@ -2207,7 +2203,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
@@ -2227,7 +2223,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
@@ -2247,7 +2243,7 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
@@ -2267,7 +2263,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
@@ -2287,7 +2283,7 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
@@ -2307,7 +2303,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
@@ -2327,7 +2323,7 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
@@ -2347,7 +2343,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
@@ -2367,7 +2363,7 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
@@ -2387,7 +2383,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
@@ -2407,7 +2403,7 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
@@ -2427,7 +2423,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
@@ -2447,7 +2443,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
@@ -2467,7 +2463,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
@@ -2487,7 +2483,7 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
@@ -2507,7 +2503,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
@@ -2527,7 +2523,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
@@ -2547,7 +2543,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
@@ -2567,7 +2563,7 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
@@ -2587,7 +2583,7 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
@@ -2607,7 +2603,7 @@
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
@@ -2627,7 +2623,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
@@ -2647,7 +2643,7 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
@@ -2667,7 +2663,7 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
@@ -2687,7 +2683,7 @@
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
@@ -2707,7 +2703,7 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
@@ -2727,7 +2723,7 @@
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
@@ -2747,7 +2743,7 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
@@ -2767,7 +2763,7 @@
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
@@ -2787,7 +2783,7 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
@@ -2807,7 +2803,7 @@
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
@@ -2827,7 +2823,7 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
@@ -2847,7 +2843,7 @@
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
@@ -2867,7 +2863,7 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
@@ -2887,7 +2883,7 @@
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
@@ -2907,7 +2903,7 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
@@ -2927,7 +2923,7 @@
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
@@ -2947,7 +2943,7 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
@@ -2967,7 +2963,7 @@
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
@@ -2987,7 +2983,7 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
@@ -3007,7 +3003,7 @@
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D57" s="14" t="n">
@@ -3027,7 +3023,7 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
@@ -3047,7 +3043,7 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
@@ -3067,7 +3063,7 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
@@ -3087,7 +3083,7 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
@@ -3107,7 +3103,7 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
@@ -3127,7 +3123,7 @@
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D63" s="14" t="n">
@@ -3147,7 +3143,7 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
@@ -3167,7 +3163,7 @@
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D65" s="14" t="n">
@@ -3187,7 +3183,7 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
@@ -3207,7 +3203,7 @@
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
@@ -3227,7 +3223,7 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
@@ -3247,7 +3243,7 @@
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
@@ -3267,7 +3263,7 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
@@ -3287,7 +3283,7 @@
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D71" s="14" t="n">
@@ -3307,7 +3303,7 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
@@ -3327,7 +3323,7 @@
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
@@ -3347,7 +3343,7 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
@@ -3430,7 +3426,7 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -3460,7 +3456,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -3490,7 +3486,7 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
